--- a/www/download/IND.abstract_labour.empe.s.mv.EXI382.xlsx
+++ b/www/download/IND.abstract_labour.empe.s.mv.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16754.465</t>
+          <t>16754464624.6072</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9597.736</t>
+          <t>9597736200.00178</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10602.33</t>
+          <t>10602330439.9958</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10614.764</t>
+          <t>10614763639.9956</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11006.706</t>
+          <t>11006706360.002</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11165.384</t>
+          <t>11165384360.0006</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11538.466</t>
+          <t>11538465813.3299</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11708.711</t>
+          <t>11708710519.9993</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>11880.586</t>
+          <t>11880585600.0021</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12263.125</t>
+          <t>12263125159.9935</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12592.446</t>
+          <t>12592445839.9989</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>13099.361</t>
+          <t>13099361079.9982</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>13550.895</t>
+          <t>13550894760.0066</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>14127.637</t>
+          <t>14127636639.9992</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14445.014</t>
+          <t>14445014480.0031</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14471.033</t>
+          <t>14471033200.0064</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>14990.991</t>
+          <t>14990991080.0003</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>15210.466</t>
+          <t>15210465919.9955</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>15346.896</t>
+          <t>15346896239.9954</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>16011.084</t>
+          <t>16011083787.5824</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>14779.538</t>
+          <t>14779537505.3079</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>15007.815</t>
+          <t>15007815165.8645</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>15410.976</t>
+          <t>15410976371.6252</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16061.608</t>
+          <t>16061608183.5885</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>15341.586</t>
+          <t>15341585690.1753</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15113.767</t>
+          <t>15113767078.3664</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>15151.871</t>
+          <t>15151870671.1626</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6423.358</t>
+          <t>6423358083.2023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3495.349</t>
+          <t>3495348999.99959</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3125.707</t>
+          <t>3125707000.00089</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5126.097</t>
+          <t>5126097000.00016</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3873.885</t>
+          <t>3873885000.00261</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4549.782</t>
+          <t>4549782270.55174</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5026.09</t>
+          <t>5026089999.99783</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5089.078</t>
+          <t>5089077999.99881</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>5368.603</t>
+          <t>5368603000.00175</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5071.931</t>
+          <t>5071931000.00152</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5422.011</t>
+          <t>5422010999.99905</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5448.219</t>
+          <t>5448218999.99835</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>5489.267</t>
+          <t>5489267000.00078</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>5459.136</t>
+          <t>5459136000.00002</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>5666.383</t>
+          <t>5666382999.99866</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5497.263</t>
+          <t>5497262999.99586</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>5549.864</t>
+          <t>5549863999.99961</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>5651.305</t>
+          <t>5651304999.99942</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>5646.745</t>
+          <t>5646744999.99829</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5613.976</t>
+          <t>5613975834.58114</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>5658.687</t>
+          <t>5658686615.67804</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5802.243</t>
+          <t>5802242841.65677</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5994.702</t>
+          <t>5994702198.71333</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6191.6</t>
+          <t>6191599976.20587</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6482.903</t>
+          <t>6482903339.92381</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>6487.264</t>
+          <t>6487263905.19797</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>6503.053</t>
+          <t>6503052694.42626</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5987.842</t>
+          <t>5987842006.70153</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3496.1</t>
+          <t>3496100000.00102</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3409.7</t>
+          <t>3409700000.00038</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3711.7</t>
+          <t>3711699999.99968</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3543999999.99785</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3250.1</t>
+          <t>3250100000.00079</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4977.2</t>
+          <t>4977200000.00014</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5052.1</t>
+          <t>5052100000.00061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5025.4</t>
+          <t>5025399999.99944</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5024.4</t>
+          <t>5024400000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5081.2</t>
+          <t>5081200000.00002</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5147.5</t>
+          <t>5147499999.99841</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>5214.6</t>
+          <t>5214599999.99965</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5319000000.00165</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>5402.8</t>
+          <t>5402800000.00127</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>5298.7</t>
+          <t>5298700000.00143</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>5348.2</t>
+          <t>5348199999.99991</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5410.5</t>
+          <t>5410500000.00227</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>5453.9</t>
+          <t>5453900000.00078</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5446.137</t>
+          <t>5446137009.22275</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>5340.488</t>
+          <t>5340488405.64894</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5482.491</t>
+          <t>5482491245.91204</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5579.218</t>
+          <t>5579217507.22453</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5692.661</t>
+          <t>5692661412.88035</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5798.441</t>
+          <t>5798440776.84077</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>5896.819</t>
+          <t>5896819136.98516</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>5907.796</t>
+          <t>5907796488.14366</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9006.52</t>
+          <t>9006519718.378</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5031.493</t>
+          <t>5031492960.00066</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4868.873</t>
+          <t>4868873359.99955</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4614.069</t>
+          <t>4614069200.00096</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4315.225</t>
+          <t>4315225200.00101</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4439.533</t>
+          <t>4439533279.99975</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4747.225</t>
+          <t>4747225080.00001</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5044.654</t>
+          <t>5044653640.00032</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5019.456</t>
+          <t>5019455999.99992</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5203.97</t>
+          <t>5203970200</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5396.679</t>
+          <t>5396679080.00092</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5520.402</t>
+          <t>5520402159.9999</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>5761.686</t>
+          <t>5761685799.9993</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>5980.152</t>
+          <t>5980151839.99816</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>6188.919</t>
+          <t>6188918840.00027</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>5827.952</t>
+          <t>5827952000.00237</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>5524.659</t>
+          <t>5524659399.99879</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>5397.443</t>
+          <t>5397443479.99868</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>5343.615</t>
+          <t>5343615159.99926</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5089.079</t>
+          <t>5089078546.48653</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>5424.965</t>
+          <t>5424964560.92309</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>5741.981</t>
+          <t>5741980723.86705</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5950.278</t>
+          <t>5950277682.53099</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6391.345</t>
+          <t>6391345192.41017</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>7029.369</t>
+          <t>7029369012.17596</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>7600.424</t>
+          <t>7600423556.28724</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>7992.322</t>
+          <t>7992321687.70886</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>123207.397</t>
+          <t>123207397216.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23230.5</t>
+          <t>23230499999.9346</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29395.2</t>
+          <t>29395199999.9367</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26256.1</t>
+          <t>26256100000.0474</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>26001.2</t>
+          <t>26001199999.9839</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>23683.6</t>
+          <t>23683600000.0281</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>31055.8</t>
+          <t>31055799999.9952</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>36697999999.9019</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>37400</t>
+          <t>37399999999.9571</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>38017.8</t>
+          <t>38017799999.9618</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>43146.5</t>
+          <t>43146500000.1162</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>44338.7</t>
+          <t>44338700000.0672</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>48761.2</t>
+          <t>48761199999.8781</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>54090.4</t>
+          <t>54090399999.9731</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>58013.6</t>
+          <t>58013600000.0157</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>61935.5</t>
+          <t>61935500000.0801</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>65611.3</t>
+          <t>65611299999.9079</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>69289.8</t>
+          <t>69289799999.9627</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>72614.5</t>
+          <t>72614499999.9771</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>134871.933</t>
+          <t>134871933012.53</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>132962.689</t>
+          <t>132962689087.825</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>110980.208</t>
+          <t>110980207708.6</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>111640.732</t>
+          <t>111640732065.247</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>126566.487</t>
+          <t>126566486934.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>113048.47</t>
+          <t>113048470498.132</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>115864.326</t>
+          <t>115864325867.508</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>111452.054</t>
+          <t>111452054264.783</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22214.536</t>
+          <t>22214535665.655</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17985.769</t>
+          <t>17985768999.9959</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16229.934</t>
+          <t>16229933999.9947</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17245.597</t>
+          <t>17245597000.0012</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17459.259</t>
+          <t>17459259000.0059</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20014.963</t>
+          <t>20014963000.0028</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20872.578</t>
+          <t>20872577999.9986</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21236.468</t>
+          <t>21236468000.0001</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21809.679</t>
+          <t>21809678999.9942</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>22109.072</t>
+          <t>22109071999.9953</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>22836.023</t>
+          <t>22836023000.0074</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>21030.285</t>
+          <t>21030284999.9982</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>23636.213</t>
+          <t>23636212999.9967</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>24020.325</t>
+          <t>24020325000.0006</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>24550.087</t>
+          <t>24550086999.9954</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>21759.22</t>
+          <t>21759219999.9987</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>24161.939</t>
+          <t>24161938999.9911</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>24734.01</t>
+          <t>24734010000.0047</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>25282.339</t>
+          <t>25282339000.0052</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>25911.377</t>
+          <t>25911377428.925</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>24044.565</t>
+          <t>24044564882.0684</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>23792.119</t>
+          <t>23792119305.7791</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>22809.74</t>
+          <t>22809740296.9647</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22699.796</t>
+          <t>22699795771.0775</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>21895.216</t>
+          <t>21895215733.6399</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23063.805</t>
+          <t>23063804983.1081</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>22526.507</t>
+          <t>22526506500.2757</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>841217.738</t>
+          <t>841217738440.014</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-669720.383</t>
+          <t>-669720383279.202</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-674520.302</t>
+          <t>-674520301520.379</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-697467.738</t>
+          <t>-697467738240.095</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-770390.921</t>
+          <t>-770390921040.211</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-798927.927</t>
+          <t>-798927927200.404</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-825401.076</t>
+          <t>-825401076240.721</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-844791.149</t>
+          <t>-844791149279.511</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-864237.414</t>
+          <t>-864237413518.904</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-846554.307</t>
+          <t>-846554307039.334</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-830577.541</t>
+          <t>-830577540520.147</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-868927.605</t>
+          <t>-868927604998.697</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-878847.702</t>
+          <t>-878847702200.154</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-825416.092</t>
+          <t>-825416091759.146</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-860126.586</t>
+          <t>-860126586280.696</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>-789376.378</t>
+          <t>-789376378438.614</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-782109.768</t>
+          <t>-782109768439.872</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>-798117.581</t>
+          <t>-798117580520.306</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-794268.834</t>
+          <t>-794268833799.972</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>357367.698</t>
+          <t>357367697504.568</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>368348.759</t>
+          <t>368348758709.098</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>474821.803</t>
+          <t>474821802624.572</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>479972.745</t>
+          <t>479972744886.273</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>503335.512</t>
+          <t>503335512220.654</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>566591.681</t>
+          <t>566591680988.07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>626464.452</t>
+          <t>626464451820.718</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>658802.493</t>
+          <t>658802493004.997</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>878.89</t>
+          <t>878889759.479918</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>289.225</t>
+          <t>289225000.000184</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>288.362</t>
+          <t>288362000.000102</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>287.766</t>
+          <t>287765999.999841</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>285.743</t>
+          <t>285743000.000079</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>279.239</t>
+          <t>279238999.999751</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>446.961</t>
+          <t>446960999.999916</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>465.886</t>
+          <t>465885999.999984</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>480.868</t>
+          <t>480868000.000102</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>488.708</t>
+          <t>488707999.99995</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>510.342</t>
+          <t>510342000.00012</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>535.657</t>
+          <t>535656999.999975</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>559.224</t>
+          <t>559223999.999988</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>603.268</t>
+          <t>603268000.000177</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>629.667</t>
+          <t>629666999.999991</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>624.836</t>
+          <t>624836000.000203</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>660.188</t>
+          <t>660188000.000062</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>661.555</t>
+          <t>661555000.000017</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>660.796</t>
+          <t>660795999.999921</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>612.347</t>
+          <t>612346650.636553</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>618.385</t>
+          <t>618384920.062959</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>651.734</t>
+          <t>651733835.924391</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>734.15</t>
+          <t>734149627.510666</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>757.545</t>
+          <t>757544973.485657</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>811.665</t>
+          <t>811664652.070503</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>852.762</t>
+          <t>852762318.369777</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>880.132</t>
+          <t>880132276.347546</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9858.675</t>
+          <t>9858675036.12063</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6316.248</t>
+          <t>6316248000.00041</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6095.142</t>
+          <t>6095142000.00138</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6389.505</t>
+          <t>6389504999.99897</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5834.972</t>
+          <t>5834971999.99839</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5908.615</t>
+          <t>5908615000.00065</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7504.379</t>
+          <t>7504379000.0012</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5564.327</t>
+          <t>5564327043.99037</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7062.057</t>
+          <t>7062057000.00103</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6744.539</t>
+          <t>6744539000.00086</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6969.614</t>
+          <t>6969614000.00098</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>7215.308</t>
+          <t>7215308000.00049</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>7246.877</t>
+          <t>7246877000.00071</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>7395.33</t>
+          <t>7395330000.00089</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>7603.847</t>
+          <t>7603847000.00119</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>7406.866</t>
+          <t>7406865999.99964</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>7361.172</t>
+          <t>7361172000.00228</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>7145.789</t>
+          <t>7145789000.00019</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>7355.161</t>
+          <t>7355160999.99984</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>6909.445</t>
+          <t>6909444627.00642</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>6668.707</t>
+          <t>6668706746.33705</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>7102.463</t>
+          <t>7102463319.85244</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>7231.422</t>
+          <t>7231422138.54233</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7714.46</t>
+          <t>7714460040.43781</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>8345.44</t>
+          <t>8345440214.73988</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>8863.747</t>
+          <t>8863747453.76591</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>8996.475</t>
+          <t>8996475230.62811</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>55896.049</t>
+          <t>55896048611.7189</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40558.5</t>
+          <t>40558499999.9997</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>39737.8</t>
+          <t>39737800000.0048</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38989.1</t>
+          <t>38989100000.0047</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>39157.1</t>
+          <t>39157099999.9859</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>39314.9</t>
+          <t>39314900000.0114</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>48835.9</t>
+          <t>48835899999.9803</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>39442.9</t>
+          <t>39442900000.0071</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>47084.195</t>
+          <t>47084194822.2647</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>46975.9</t>
+          <t>46975900000.0133</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>46377.1</t>
+          <t>46377100000.0077</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>42942.6</t>
+          <t>42942599999.9878</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>47232</t>
+          <t>47231999999.9976</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>48199</t>
+          <t>48198999999.9895</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>48696999999.984</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>46934.8</t>
+          <t>46934800000</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>47845.2</t>
+          <t>47845199999.9889</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48702</t>
+          <t>48701999999.9996</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>48736</t>
+          <t>48735999999.9936</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>49393.718</t>
+          <t>49393718414.1668</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>51172.842</t>
+          <t>51172841709.8672</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>50768.709</t>
+          <t>50768709051.4442</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>51327.958</t>
+          <t>51327957926.849</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>54426.214</t>
+          <t>54426213572.8534</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>53168.715</t>
+          <t>53168714510.3535</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>53749.309</t>
+          <t>53749308582.7953</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>55620.992</t>
+          <t>55620991634.2714</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4874.13</t>
+          <t>4874129751.86717</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4526.904</t>
+          <t>4526903999.99936</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4543.232</t>
+          <t>4543232000.00006</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4332.852</t>
+          <t>4332852000.00016</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3859.281</t>
+          <t>3859281000.00012</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4943.423</t>
+          <t>4943422999.99928</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4735.495</t>
+          <t>4735494793.43733</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4857.539</t>
+          <t>4857538999.99961</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4920.819</t>
+          <t>4920819000.00106</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4799.586</t>
+          <t>4799585682.25798</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4808.336</t>
+          <t>4808335503.13213</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4751.638</t>
+          <t>4751637999.99896</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>5265.187</t>
+          <t>5265186999.99996</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>5277.768</t>
+          <t>5277768000.00128</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>5106.672</t>
+          <t>5106671999.99947</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>4843.766</t>
+          <t>4843766000.00074</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>4831.166</t>
+          <t>4831166000.00193</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4830.285</t>
+          <t>4830285000.00042</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>4785.396</t>
+          <t>4785395999.99953</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>4900.88</t>
+          <t>4900880285.63519</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>5179.014</t>
+          <t>5179013596.65242</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5006.276</t>
+          <t>5006276288.53234</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>5020.564</t>
+          <t>5020564160.97487</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5046.368</t>
+          <t>5046368445.80708</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>4689.262</t>
+          <t>4689261956.29045</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>4625.921</t>
+          <t>4625920600.32929</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>4638.435</t>
+          <t>4638435225.0836</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>35102.265</t>
+          <t>35102265442.6347</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23968.008</t>
+          <t>23968008000.0011</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24266.114</t>
+          <t>24266113999.9976</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25277.577</t>
+          <t>25277577000.0066</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26479.914</t>
+          <t>26479914000.006</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>28985.396</t>
+          <t>28985395999.999</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>29768.741</t>
+          <t>29768741000.0081</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30993.92</t>
+          <t>30993919999.9957</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>32457.008</t>
+          <t>32457008000.002</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>33253.823</t>
+          <t>33253823000.0027</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>34980.467</t>
+          <t>34980466999.9994</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>38186.063</t>
+          <t>38186063000.0063</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>40378.747</t>
+          <t>40378747000.0014</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>41522.652</t>
+          <t>41522651999.9951</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>40078.343</t>
+          <t>40078343000.0034</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>36714.646</t>
+          <t>36714645788.2233</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>35886.87</t>
+          <t>35886869999.9896</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>35142.813</t>
+          <t>35142812999.9948</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>32348.009</t>
+          <t>32348009486.0509</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>31976.794</t>
+          <t>31976793663.9366</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>31623.479</t>
+          <t>31623478998.8638</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>33021.182</t>
+          <t>33021182461.5269</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>33435.679</t>
+          <t>33435679307.9756</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>33759.379</t>
+          <t>33759378945.4186</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>34507.019</t>
+          <t>34507018869.7443</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>34303.23</t>
+          <t>34303230035.0241</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>35044.413</t>
+          <t>35044412821.5279</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2452.01</t>
+          <t>2452009862.35184</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1079.21</t>
+          <t>1079210000.00013</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1010.778</t>
+          <t>1010778000.00025</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1000.963</t>
+          <t>1000962999.99971</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>995.141</t>
+          <t>995140999.999945</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>930.136</t>
+          <t>930136000.00013</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>986.949</t>
+          <t>986948999.999764</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>977.552</t>
+          <t>977552000.000037</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1011.718</t>
+          <t>1011718000.00023</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>979.287</t>
+          <t>979286999.999754</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>981.078</t>
+          <t>981078000.000094</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1053.596</t>
+          <t>1053595999.99976</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1224.73</t>
+          <t>1224730000.00013</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1221.132</t>
+          <t>1221132000.00005</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1239.102</t>
+          <t>1239102000</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1074.69</t>
+          <t>1074689999.99971</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1050.721</t>
+          <t>1050721000.00001</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1115.046</t>
+          <t>1115046000.0001</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1126.911</t>
+          <t>1126911000.00025</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1162.089</t>
+          <t>1162089372.578</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1109.894</t>
+          <t>1109894100.99148</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>1141.746</t>
+          <t>1141746181.74502</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>1208.665</t>
+          <t>1208664599.97612</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1236.614</t>
+          <t>1236614310.54454</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1360.584</t>
+          <t>1360583989.76733</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>1469.568</t>
+          <t>1469567832.97889</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1495.462</t>
+          <t>1495461996.9513</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3734.219</t>
+          <t>3734219025.22882</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2586.159</t>
+          <t>2586159000.00004</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2492.024</t>
+          <t>2492023999.99807</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2848.493</t>
+          <t>2848492999.99927</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2884.092</t>
+          <t>2884092000.00033</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3111.362</t>
+          <t>3111361999.99875</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3158.356</t>
+          <t>3158355999.99828</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3233.126</t>
+          <t>3233125999.99917</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3274.489</t>
+          <t>3274489000.00058</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3213.937</t>
+          <t>3213936999.99859</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3304.032</t>
+          <t>3304032000.00004</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3421.877</t>
+          <t>3421877000.00076</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4182.388</t>
+          <t>4182387999.99967</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>4261.447</t>
+          <t>4261446999.99949</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3853.173</t>
+          <t>3853172999.9995</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>3172.753</t>
+          <t>3172753000.00073</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>3934.829</t>
+          <t>3934828999.99868</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3972.848</t>
+          <t>3972848000.00034</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>3212.122</t>
+          <t>3212122000.00164</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3801.748</t>
+          <t>3801748032.30918</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>3815.19</t>
+          <t>3815189832.69623</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>3814.434</t>
+          <t>3814434278.28516</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>3836.942</t>
+          <t>3836942275.78514</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3841.651</t>
+          <t>3841651010.92335</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>4051.951</t>
+          <t>4051951028.89277</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>3867.751</t>
+          <t>3867751166.44312</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3904.434</t>
+          <t>3904433576.57089</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>31005.95</t>
+          <t>31005949928.19</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21982.7</t>
+          <t>21982699999.9956</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>26108.7</t>
+          <t>26108699999.9985</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>26337.9</t>
+          <t>26337900000.0054</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19995.2</t>
+          <t>19995200000.0087</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27841.7</t>
+          <t>27841700000.0133</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27962.4</t>
+          <t>27962399999.9986</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28493.6</t>
+          <t>28493600000.004</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>28063.1</t>
+          <t>28063099999.9939</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>28001.6</t>
+          <t>28001600000.0089</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>28561.2</t>
+          <t>28561200000.0053</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>28649.9</t>
+          <t>28649899999.9855</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>34052.5</t>
+          <t>34052500000.0009</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>34960.3</t>
+          <t>34960300000.01</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>35343.2</t>
+          <t>35343200000.0037</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>28955.9</t>
+          <t>28955900000.0171</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>34548.7</t>
+          <t>34548699999.9907</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>30437.158</t>
+          <t>30437158187.5278</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>28915.8</t>
+          <t>28915800000.0085</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>33134.827</t>
+          <t>33134827014.6083</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>33202.866</t>
+          <t>33202865674.0473</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>33068.719</t>
+          <t>33068719088.941</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>32395.859</t>
+          <t>32395859309.594</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>30987.237</t>
+          <t>30987236837.7582</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>31878.549</t>
+          <t>31878549090.6707</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>31948.955</t>
+          <t>31948955147.3682</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>31557.836</t>
+          <t>31557836016.6576</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>53093.213</t>
+          <t>53093212944.5983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>35062.833</t>
+          <t>35062832999.9873</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>36857.662</t>
+          <t>36857662000.0008</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>37485.382</t>
+          <t>37485382000.0066</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>38745.291</t>
+          <t>38745291000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>38228.534</t>
+          <t>38228533999.9899</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>39187.488</t>
+          <t>39187488000.002</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>37377.664</t>
+          <t>37377664000.0033</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>39840.172</t>
+          <t>39840171999.9967</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>39444.429</t>
+          <t>39444429000.003</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>39186.602</t>
+          <t>39186602000.0179</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>40482.728</t>
+          <t>40482728000.0097</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>40438.905</t>
+          <t>40438904999.9918</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>40909.13</t>
+          <t>40909130000.0037</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>38821.163</t>
+          <t>38821162999.995</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>37710.491</t>
+          <t>37710490999.9922</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>37225.327</t>
+          <t>37225327000.0061</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>37362.742</t>
+          <t>37362742000.0054</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>37472.16</t>
+          <t>37472160000</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>45302.259</t>
+          <t>45302259332.5548</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>49118.627</t>
+          <t>49118627134.4842</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>56528.594</t>
+          <t>56528593751.3536</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>49986.636</t>
+          <t>49986635907.1867</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>48155.831</t>
+          <t>48155830532.5504</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>50425.512</t>
+          <t>50425512047.352</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>52434.268</t>
+          <t>52434267542.0527</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>52741.382</t>
+          <t>52741381965.7925</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4203.683</t>
+          <t>4203683402.51277</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>126.283</t>
+          <t>126282999.996913</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>184.024</t>
+          <t>184023999.99978</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>309.592</t>
+          <t>309591999.999228</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>560.613</t>
+          <t>560613000.003446</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>837.343</t>
+          <t>837342999.998655</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>974.885</t>
+          <t>974884999.997845</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1344.94</t>
+          <t>1344939999.99721</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1431.205</t>
+          <t>1431205000.0003</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1478.552</t>
+          <t>1478551999.99934</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1963.929</t>
+          <t>1963928999.99975</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025.122</t>
+          <t>2025122000.00002</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>5927.617</t>
+          <t>5927616999.99859</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>6038.021</t>
+          <t>6038021000.00276</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>6072.191</t>
+          <t>6072190999.99713</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2158.263</t>
+          <t>2158262999.99928</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>5676.534</t>
+          <t>5676534000.0005</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1647.782</t>
+          <t>1647782000.00088</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1331.109</t>
+          <t>1331108999.99764</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>4425.532</t>
+          <t>4425532136.39581</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>4110.718</t>
+          <t>4110718014.36065</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>4053.618</t>
+          <t>4053617712.86537</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>3847.049</t>
+          <t>3847048855.40794</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3963.208</t>
+          <t>3963208192.63853</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3971.431</t>
+          <t>3971430536.74952</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>4028.577</t>
+          <t>4028576985.33781</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>4016.035</t>
+          <t>4016034802.06838</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9249.801</t>
+          <t>9249801424.26949</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7903.516</t>
+          <t>7903516000.00021</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7699.552</t>
+          <t>7699551999.9997</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7770.26</t>
+          <t>7770260000.0006</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7873.157</t>
+          <t>7873156999.9987</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8196.551</t>
+          <t>8196551000.00013</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7879.036</t>
+          <t>7879035999.99921</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8328.109</t>
+          <t>8328109000.00005</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7971.619</t>
+          <t>7971618999.99858</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8322.943</t>
+          <t>8322942999.9994</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8283.253</t>
+          <t>8283252999.99875</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8103.059</t>
+          <t>8103059000.00083</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>8400.355</t>
+          <t>8400354999.99996</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>8334.356</t>
+          <t>8334356000.00052</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>7886.61</t>
+          <t>7886609999.99904</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>7706.64</t>
+          <t>7706640000.0003</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>7726.319</t>
+          <t>7726319000.00005</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>7691.758</t>
+          <t>7691758000.00065</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>7739.7</t>
+          <t>7739699999.99885</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>7602.732</t>
+          <t>7602732180.04816</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>7602.527</t>
+          <t>7602527327.31525</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>8015.414</t>
+          <t>8015413899.38027</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>7915.241</t>
+          <t>7915241069.34876</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>8506.673</t>
+          <t>8506673352.04753</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>9079.161</t>
+          <t>9079160701.73161</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>9404.711</t>
+          <t>9404710591.2319</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>9610.98</t>
+          <t>9610980444.13418</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>218668.892</t>
+          <t>218668892382.824</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-684162.367</t>
+          <t>-684162367000.679</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-708744.779</t>
+          <t>-708744779000.323</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-707456.424</t>
+          <t>-707456424000.536</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-690146.528</t>
+          <t>-690146527999.599</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-716886.671</t>
+          <t>-716886670999.68</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-769972.613</t>
+          <t>-769972612999.931</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-764221.541</t>
+          <t>-764221540999.341</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-750088.931</t>
+          <t>-750088930999.408</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-763188.242</t>
+          <t>-763188241999.723</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-769075.409</t>
+          <t>-769075409001.259</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-767338.005</t>
+          <t>-767338005000.157</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-753850.91</t>
+          <t>-753850910000.665</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-755363.919</t>
+          <t>-755363918999.853</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-756265.84</t>
+          <t>-756265839999.424</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-757918.461</t>
+          <t>-757918460999.716</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-757676.757</t>
+          <t>-757676756999.878</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>-764052.369</t>
+          <t>-764052368999.593</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>-768659.287</t>
+          <t>-768659286999.45</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>76833.768</t>
+          <t>76833767631.6711</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>90370.628</t>
+          <t>90370627581.5568</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>120510.651</t>
+          <t>120510650732.627</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>133172.236</t>
+          <t>133172236365.528</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>148406.821</t>
+          <t>148406821426.831</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>153042.666</t>
+          <t>153042666272.94</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>166013.739</t>
+          <t>166013738560.873</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>174456.364</t>
+          <t>174456363612.896</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>160644.883</t>
+          <t>160644882758.964</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-24870.244</t>
+          <t>-24870243999.9623</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-30795.088</t>
+          <t>-30795087999.906</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-28501.217</t>
+          <t>-28501216999.9436</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-33981.239</t>
+          <t>-33981238999.9296</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-33487.158</t>
+          <t>-33487158000.0511</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-39323.505</t>
+          <t>-39323505000.119</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-41397.884</t>
+          <t>-41397884000.0129</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-44035.325</t>
+          <t>-44035325000.1183</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-46045.971</t>
+          <t>-46045971000.0686</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-47202.77</t>
+          <t>-47202770000.0392</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-45180.136</t>
+          <t>-45180135999.9509</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-44497.813</t>
+          <t>-44497812999.9388</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-53237.904</t>
+          <t>-53237903999.9777</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-47949.677</t>
+          <t>-47949677000.0199</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>-45485.336</t>
+          <t>-45485336000.0432</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>-41719.771</t>
+          <t>-41719770999.9957</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>-40200.173</t>
+          <t>-40200173000.0135</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>-32977.008</t>
+          <t>-32977008000.0858</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>97708.111</t>
+          <t>97708111258.489</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>95205.135</t>
+          <t>95205135220.2527</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>111099.72</t>
+          <t>111099720091.216</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>117822.911</t>
+          <t>117822910751.485</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>115894.177</t>
+          <t>115894177034.354</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>113474.093</t>
+          <t>113474092730.146</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>127061.319</t>
+          <t>127061319387.173</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>134139.702</t>
+          <t>134139702391.264</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5197.415</t>
+          <t>5197415303.93221</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>945.711</t>
+          <t>945711000.000445</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1199.045</t>
+          <t>1199045000.0001</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1261.275</t>
+          <t>1261274999.99964</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1343.094</t>
+          <t>1343093999.99964</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1604.064</t>
+          <t>1604064000.00078</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1692.979</t>
+          <t>1692978999.99971</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1846.39</t>
+          <t>1846389999.99947</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1814.813</t>
+          <t>1814812999.99949</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1919.615</t>
+          <t>1919614999.99971</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1921.2</t>
+          <t>1921200000.00051</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2150.668</t>
+          <t>2150668000.00062</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>3125.051</t>
+          <t>3125050999.99975</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3184.546</t>
+          <t>3184546000.00007</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2609.114</t>
+          <t>2609113929.4304</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1933.484</t>
+          <t>1933483999.99974</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2020.989</t>
+          <t>2020989000.00059</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2021.051</t>
+          <t>2021050999.99947</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1886.364</t>
+          <t>1886363999.9992</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2749.425</t>
+          <t>2749424599.30714</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2857.729</t>
+          <t>2857728841.31306</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>3708.718</t>
+          <t>3708718492.27492</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>4108.133</t>
+          <t>4108133417.38389</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4096.028</t>
+          <t>4096027513.20308</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>4313.811</t>
+          <t>4313811152.4307</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>4680.31</t>
+          <t>4680310247.68454</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>4987.182</t>
+          <t>4987181883.50511</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>32965.059</t>
+          <t>32965058780.2349</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15256.702</t>
+          <t>15256701999.9944</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14869.773</t>
+          <t>14869772999.9994</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15366.869</t>
+          <t>15366869000.0011</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15468.39</t>
+          <t>15468389999.9934</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16111.105</t>
+          <t>16111105000.0058</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16412.412</t>
+          <t>16412411999.9946</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16907.525</t>
+          <t>16907524999.9971</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>15749.482</t>
+          <t>15749481999.9952</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>18018.585</t>
+          <t>18018584999.993</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>17606.361</t>
+          <t>17606360999.999</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>18786.101</t>
+          <t>18786101000.0043</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>33100.231</t>
+          <t>33100231000.0161</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>33466.172</t>
+          <t>33466172000.0071</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>19689.855</t>
+          <t>19689854999.9952</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>19558.874</t>
+          <t>19558873999.9956</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>19384.964</t>
+          <t>19384963999.9982</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>19582.351</t>
+          <t>19582350999.989</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>19397.416</t>
+          <t>19397415999.9869</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>30475.362</t>
+          <t>30475362293.7934</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>30586.541</t>
+          <t>30586541132.9788</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>30921.886</t>
+          <t>30921886106.6731</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>31156.588</t>
+          <t>31156588130.605</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>31482.167</t>
+          <t>31482167069.4489</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>32850.18</t>
+          <t>32850180392.2562</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>32037.56</t>
+          <t>32037560455.9335</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>32735.886</t>
+          <t>32735885606.9028</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>88458.448</t>
+          <t>88458448492.7047</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>91504.531</t>
+          <t>91504531000.0381</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>93346.987</t>
+          <t>93346987000.0294</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>94590.89</t>
+          <t>94590889999.9933</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>94538.248</t>
+          <t>94538247999.9995</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>94104.871</t>
+          <t>94104870999.9994</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>95336.201</t>
+          <t>95336200999.9727</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96427.936</t>
+          <t>96427936000.0365</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>96057.136</t>
+          <t>96057135999.9963</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>96469.953</t>
+          <t>96469952999.9986</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>96930.934</t>
+          <t>96930934000.022</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>97508.772</t>
+          <t>97508771999.9549</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>100568.604</t>
+          <t>100568603999.982</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>101784.846</t>
+          <t>101784846000.014</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>102284.141</t>
+          <t>102284140999.995</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>98067.684</t>
+          <t>98067684000.0033</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>98722.52</t>
+          <t>98722520000.0185</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>99097.518</t>
+          <t>99097517999.9505</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>98941.44</t>
+          <t>98941440000.0128</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>88838.03</t>
+          <t>88838029567.2216</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>88650.991</t>
+          <t>88650990538.4053</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>91689.867</t>
+          <t>91689866953.2304</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>97495.336</t>
+          <t>97495335933.547</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>90666.051</t>
+          <t>90666050996.3481</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>89691.192</t>
+          <t>89691191739.4495</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>95280.071</t>
+          <t>95280070858.6335</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>94388.316</t>
+          <t>94388316191.7448</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>63979.516</t>
+          <t>63979515598.4278</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12546.9</t>
+          <t>12546899999.9982</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12965.635</t>
+          <t>12965635000.0012</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13031.732</t>
+          <t>13031731999.9842</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>10644.773</t>
+          <t>10644773000.0072</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11519.299</t>
+          <t>11519299000.0118</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13495.613</t>
+          <t>13495613000.0174</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13935.695</t>
+          <t>13935694999.9791</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14930.33</t>
+          <t>14930329999.9935</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>15963.491</t>
+          <t>15963491000.0049</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17258.712</t>
+          <t>17258711999.9949</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>17932.969</t>
+          <t>17932968999.9945</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>18992.347</t>
+          <t>18992347000.0068</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>20735.217</t>
+          <t>20735216999.9864</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>21009.087</t>
+          <t>21009086999.9898</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>22212.254</t>
+          <t>22212254000.0247</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>23517.883</t>
+          <t>23517882999.9935</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>24545.701</t>
+          <t>24545700999.9974</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>24995.408</t>
+          <t>24995408000.004</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>39652.84</t>
+          <t>39652840230.6264</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>47984.688</t>
+          <t>47984688372.7543</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>55827.931</t>
+          <t>55827931409.3387</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>55856.191</t>
+          <t>55856191457.3595</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>57382.663</t>
+          <t>57382663432.8317</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>57759.799</t>
+          <t>57759799329.0183</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>57516.397</t>
+          <t>57516396599.2253</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>57720.477</t>
+          <t>57720477029.7115</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3499.116</t>
+          <t>3499116085.38316</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1951.345</t>
+          <t>1951345000.00024</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1916.662</t>
+          <t>1916661999.99846</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1990.543</t>
+          <t>1990542999.99992</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2018.087</t>
+          <t>2018086999.99899</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2075.033</t>
+          <t>2075033000.00084</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1935.085</t>
+          <t>1935085000.00027</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1768.467</t>
+          <t>1768466999.99948</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1790.512</t>
+          <t>1790511999.99933</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1842.923</t>
+          <t>1842923000.00012</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1877.44</t>
+          <t>1877439999.99919</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2060.236</t>
+          <t>2060235999.99879</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2295.932</t>
+          <t>2295932117.35151</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2646.236</t>
+          <t>2646236000.00031</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2264.985</t>
+          <t>2264984999.99999</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2052.444</t>
+          <t>2052444000.00013</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2005.067</t>
+          <t>2005066999.99958</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2007.635</t>
+          <t>2007634999.9997</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2015.492</t>
+          <t>2015492000.00049</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2333.276</t>
+          <t>2333275603.48973</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2402.843</t>
+          <t>2402843436.97171</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2463.579</t>
+          <t>2463579386.96312</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2534.949</t>
+          <t>2534949461.59891</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2722.3</t>
+          <t>2722300090.4994</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>3000.496</t>
+          <t>3000496462.34438</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>3074.567</t>
+          <t>3074567107.60368</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>3211.551</t>
+          <t>3211550610.05296</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>595.778</t>
+          <t>595777610.942204</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>229.958</t>
+          <t>229958000.000042</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>248.788</t>
+          <t>248787999.99994</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>255.993</t>
+          <t>255992999.999925</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>245.256</t>
+          <t>245256000.00004</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>261.889</t>
+          <t>261889000.000089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>265.623</t>
+          <t>265623000.000073</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>294.184</t>
+          <t>294184000.000031</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>291.053</t>
+          <t>291053000.000056</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>277.33</t>
+          <t>277329999.99991</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>280.268</t>
+          <t>280268000.000107</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>285.845</t>
+          <t>285844999.999891</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>298.127</t>
+          <t>298127000</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>326.732</t>
+          <t>326732000.000006</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>306.412</t>
+          <t>306411999.99999</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>312.941</t>
+          <t>312940999.999984</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>319.241</t>
+          <t>319241000.000067</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>324.538</t>
+          <t>324538000.000132</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>341.931</t>
+          <t>341931000.000055</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>403.663</t>
+          <t>403663231.002174</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>460.432</t>
+          <t>460432475.107833</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>488.385</t>
+          <t>488384873.64935</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>504.299</t>
+          <t>504298959.841828</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>504.926</t>
+          <t>504926079.304224</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>516.499</t>
+          <t>516498636.369573</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>544.936</t>
+          <t>544935618.470873</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>560.597</t>
+          <t>560596539.605667</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2482.216</t>
+          <t>2482216265.72787</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1295.763</t>
+          <t>1295763000.00032</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1413.372</t>
+          <t>1413371999.9997</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1450.843</t>
+          <t>1450842999.99928</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1384.943</t>
+          <t>1384943000.00073</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1506.815</t>
+          <t>1506814999.9995</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1561.965</t>
+          <t>1561964999.99967</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1595.346</t>
+          <t>1595345999.99932</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1750.087</t>
+          <t>1750087000.00023</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1749.95</t>
+          <t>1749949999.99952</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1746.657</t>
+          <t>1746656999.99973</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1863.841</t>
+          <t>1863841000.00029</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1946.868</t>
+          <t>1946868000.00004</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1832.046</t>
+          <t>1832046000.00036</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1791.426</t>
+          <t>1791426000.00056</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1469.006</t>
+          <t>1469006000.00035</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1366.186</t>
+          <t>1366185999.99976</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1262.17</t>
+          <t>1262170000.00013</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1373.036</t>
+          <t>1373036000.00011</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1698.619</t>
+          <t>1698618673.20662</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>1619.831</t>
+          <t>1619830947.6713</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>1802.726</t>
+          <t>1802725797.06564</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1708.058</t>
+          <t>1708057658.63376</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>1936.419</t>
+          <t>1936419320.28309</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2066.989</t>
+          <t>2066989403.51473</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2065.269</t>
+          <t>2065268818.75981</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>2124.189</t>
+          <t>2124189203.40553</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>119859.165</t>
+          <t>119859165041.781</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10129.794</t>
+          <t>10129793999.9994</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13725.005</t>
+          <t>13725004999.9792</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>13760.457</t>
+          <t>13760456999.9863</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>17575.637</t>
+          <t>17575636999.9589</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>19230.906</t>
+          <t>19230905999.9865</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>22880.51</t>
+          <t>22880509999.9617</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>22018.721</t>
+          <t>22018720999.9896</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>22171.321</t>
+          <t>22171321000.0323</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>22438.295</t>
+          <t>22438295000.0217</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>23771.831</t>
+          <t>23771831000.0259</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>25300.633</t>
+          <t>25300633000.0687</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>28123.928</t>
+          <t>28123927999.9577</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>28829.067</t>
+          <t>28829066999.9896</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>30593.764</t>
+          <t>30593763999.9243</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>47248.538</t>
+          <t>47248537999.9497</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>63967.049</t>
+          <t>63967049000.0046</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>33603.937</t>
+          <t>33603937000.0113</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>34804.515</t>
+          <t>34804515000.0256</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>76941.775</t>
+          <t>76941774730.7342</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>89456.267</t>
+          <t>89456266633.7735</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>85583.005</t>
+          <t>85583004949.6026</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>73017.892</t>
+          <t>73017892171.2759</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>87639.856</t>
+          <t>87639855701.5156</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>90996.664</t>
+          <t>90996663801.995</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>100173.787</t>
+          <t>100173786779.859</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>103350.219</t>
+          <t>103350218540.553</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>586.245</t>
+          <t>586244584.236512</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>211.82</t>
+          <t>211819999.999972</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>237.596</t>
+          <t>237596000.000005</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>244.487</t>
+          <t>244487000.000024</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>247.484</t>
+          <t>247484000.000042</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>250.635</t>
+          <t>250635000.000048</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>252.948</t>
+          <t>252947999.999932</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>213.68</t>
+          <t>213679999.999994</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>224.842</t>
+          <t>224842000.000041</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>221.821</t>
+          <t>221820999.999971</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>219.561</t>
+          <t>219561000.000002</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>222.454</t>
+          <t>222454000.000033</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>216.145</t>
+          <t>216145000.000042</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>232.939</t>
+          <t>232938999.999965</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>226.437</t>
+          <t>226436999.999995</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>227.403</t>
+          <t>227403000.000017</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>222.139</t>
+          <t>222138999.999891</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>233.119</t>
+          <t>233118999.9999</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>239.259</t>
+          <t>239259000.000029</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>314.033</t>
+          <t>314032921.288966</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>357.924</t>
+          <t>357923855.197612</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>384.526</t>
+          <t>384526079.005162</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>413.253</t>
+          <t>413252524.347764</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>460.535</t>
+          <t>460535040.917698</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>520.198</t>
+          <t>520197798.344928</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>545.449</t>
+          <t>545449475.949108</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>560.125</t>
+          <t>560125194.897939</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>12202.995</t>
+          <t>12202994765.6581</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7425.578</t>
+          <t>7425578000.00124</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8156.605</t>
+          <t>8156605000.00035</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>8431.127</t>
+          <t>8431127000.00051</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8924.724</t>
+          <t>8924724000.00115</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9068.079</t>
+          <t>9068078999.99772</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9248.854</t>
+          <t>9248853999.99984</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>9516.986</t>
+          <t>9516985999.99758</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8876.196</t>
+          <t>8876195999.99981</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>9616.107</t>
+          <t>9616106999.9998</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9147.307</t>
+          <t>9147307000.00216</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>9476.798</t>
+          <t>9476797999.99786</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>9639.301</t>
+          <t>9639301000.00131</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>9602.604</t>
+          <t>9602604000.00086</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>9239.825</t>
+          <t>9239825000.00509</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>8978.902</t>
+          <t>8978901999.99942</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>8182.999</t>
+          <t>8182998999.99629</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>8198.201</t>
+          <t>8198200999.99876</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>8140.528</t>
+          <t>8140527999.99898</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>9961.397</t>
+          <t>9961396916.99811</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>10020.925</t>
+          <t>10020924639.7322</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>9846.405</t>
+          <t>9846404686.02831</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>9723.526</t>
+          <t>9723525767.40281</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10022.39</t>
+          <t>10022389809.332</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>10118.114</t>
+          <t>10118113575.7378</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10221.229</t>
+          <t>10221228754.2516</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>10243.9</t>
+          <t>10243899923.8036</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>33072.527</t>
+          <t>33072526502.9976</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13024.295</t>
+          <t>13024294999.9918</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13333.651</t>
+          <t>13333651000.0127</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>13550.062</t>
+          <t>13550061999.9849</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13772.151</t>
+          <t>13772150999.987</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>13578.996</t>
+          <t>13578996000.0064</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14221.017</t>
+          <t>14221016999.9951</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>13589.27</t>
+          <t>13589269999.9987</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>12809.316</t>
+          <t>12809315999.9923</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>13178.183</t>
+          <t>13178182999.999</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>13490.67</t>
+          <t>13490669999.9989</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>14847.515</t>
+          <t>14847514999.9942</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>16177.137</t>
+          <t>16177137000.0047</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>17466.637</t>
+          <t>17466636999.9861</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>17582.644</t>
+          <t>17582644000.0074</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>17682.965</t>
+          <t>17682964999.998</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>17188.821</t>
+          <t>17188820999.9983</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>17213.187</t>
+          <t>17213187000.0124</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>17386.694</t>
+          <t>17386694000.0054</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>24504.197</t>
+          <t>24504197285.2483</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>24767.304</t>
+          <t>24767303680.209</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>25779.87</t>
+          <t>25779869801.3746</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>24658.969</t>
+          <t>24658968929.5853</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>26678.398</t>
+          <t>26678397955.929</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>27571.841</t>
+          <t>27571841010.7937</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>29518.034</t>
+          <t>29518034458.383</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>30813.972</t>
+          <t>30813971664.9689</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7985.88</t>
+          <t>7985880157.56661</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3749.342</t>
+          <t>3749342000.0004</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3650.307</t>
+          <t>3650307000.00171</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3737.373</t>
+          <t>3737372999.99866</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3980.436</t>
+          <t>3980436000.00006</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4372.957</t>
+          <t>4372956999.99797</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4506.281</t>
+          <t>4506280999.99978</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4562.734</t>
+          <t>4562734000.00106</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4650.451</t>
+          <t>4650450999.99968</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4527.357</t>
+          <t>4527356999.99899</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>4784.524</t>
+          <t>4784523999.99986</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4780.259</t>
+          <t>4780259000.00173</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>5067.009</t>
+          <t>5067008999.99694</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>5045.598</t>
+          <t>5045598000.00147</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>5075.359</t>
+          <t>5075358999.99979</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>5010.567</t>
+          <t>5010567000.00059</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>5231.546</t>
+          <t>5231545999.99509</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>5327.315</t>
+          <t>5327315000.00114</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>5019.011</t>
+          <t>5019011000.00062</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>7062.971</t>
+          <t>7062971356.42953</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>7020.989</t>
+          <t>7020989140.61283</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>7100.891</t>
+          <t>7100891039.77533</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>7189.168</t>
+          <t>7189168146.71975</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>7597.191</t>
+          <t>7597191297.72135</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>7767.92</t>
+          <t>7767919689.91955</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>7913.817</t>
+          <t>7913816524.12526</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>8006.393</t>
+          <t>8006392992.89574</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>24668.974</t>
+          <t>24668974339.7342</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5835.129</t>
+          <t>5835128999.98306</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5024.472</t>
+          <t>5024471999.99089</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5729.654</t>
+          <t>5729654000.00001</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5730.634</t>
+          <t>5730633999.99378</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4615.718</t>
+          <t>4615718000.00198</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3600.745</t>
+          <t>3600744999.99881</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2929.859</t>
+          <t>2929859000.00766</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4680.224</t>
+          <t>4680224000.00444</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>4496.728</t>
+          <t>4496728000.00799</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>7033.792</t>
+          <t>7033792000.00615</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6308.701</t>
+          <t>6308700999.99699</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>7504.368</t>
+          <t>7504368000.00686</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>7762.269</t>
+          <t>7762268999.98967</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>7860.876</t>
+          <t>7860876000.00922</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>7605.19</t>
+          <t>7605190000.00318</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>5991.702</t>
+          <t>5991701999.98958</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>6595.933</t>
+          <t>6595933000.00161</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>6970.37</t>
+          <t>6970370000.00348</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>13761.899</t>
+          <t>13761899334.3404</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>14520.096</t>
+          <t>14520095698.3847</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>16370.961</t>
+          <t>16370961389.7685</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>17160.714</t>
+          <t>17160713775.0157</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20311.628</t>
+          <t>20311628488.7868</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>22092.111</t>
+          <t>22092110667.5886</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>22441.775</t>
+          <t>22441775300.9552</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>22894.987</t>
+          <t>22894987278.4134</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>125819.217</t>
+          <t>125819217334.405</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>106112.071</t>
+          <t>106112071000.016</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>106402.489</t>
+          <t>106402489000.009</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>104563.688</t>
+          <t>104563688000.011</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>103401.592</t>
+          <t>103401591999.999</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>96937.194</t>
+          <t>96937193999.99</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>102256.503</t>
+          <t>102256503000.017</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>107285.466</t>
+          <t>107285466000.042</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>110757.119</t>
+          <t>110757119000.023</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>111603.658</t>
+          <t>111603657999.989</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>103534.079</t>
+          <t>103534079000.001</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>113821.915</t>
+          <t>113821914999.987</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>115532.259</t>
+          <t>115532258999.997</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>119140.747</t>
+          <t>119140746999.983</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>112582.512</t>
+          <t>112582512000.032</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>116548.748</t>
+          <t>116548748000.006</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>119701.33</t>
+          <t>119701330000.008</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>109476.638</t>
+          <t>109476637999.997</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>122684.004</t>
+          <t>122684004000.041</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>135370.034</t>
+          <t>135370033843.919</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>117564.097</t>
+          <t>117564096918.719</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>94573.966</t>
+          <t>94573966155.9576</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>89302.92</t>
+          <t>89302920343.8432</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>106839.526</t>
+          <t>106839525985.053</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>106448.721</t>
+          <t>106448721275.037</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>114332.347</t>
+          <t>114332346864.228</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>116475.636</t>
+          <t>116475636221.617</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6233.695</t>
+          <t>6233694507.90817</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4769.835</t>
+          <t>4769835000.00089</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4935.474</t>
+          <t>4935474000.00013</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4921.569</t>
+          <t>4921569000.00004</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4781.274</t>
+          <t>4781273999.9994</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4724.386</t>
+          <t>4724385999.9992</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4559.328</t>
+          <t>4559328000.0004</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4512.368</t>
+          <t>4512367999.99995</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4555.518</t>
+          <t>4555517999.9994</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>4647.109</t>
+          <t>4647109000.00173</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>4569.028</t>
+          <t>4569027999.99989</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>4747.425</t>
+          <t>4747424999.99924</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>4744.027</t>
+          <t>4744026999.99968</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>4950.275</t>
+          <t>4950275000.00029</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>4792.477</t>
+          <t>4792476999.99911</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>4651.383</t>
+          <t>4651382999.99893</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>4562.405</t>
+          <t>4562404999.99933</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>4577.578</t>
+          <t>4577577999.99858</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>4608.85</t>
+          <t>4608849999.99972</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>4618.911</t>
+          <t>4618910879.38799</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>4683.65</t>
+          <t>4683650204.48756</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>4915.401</t>
+          <t>4915401399.65194</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>4769.513</t>
+          <t>4769513045.76214</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>5116.14</t>
+          <t>5116140260.5228</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>5172.893</t>
+          <t>5172893032.59962</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>5339.802</t>
+          <t>5339801645.94227</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>5654.551</t>
+          <t>5654551030.18936</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1487.721</t>
+          <t>1487721296.88622</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1237.153</t>
+          <t>1237153000.00049</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1224.756</t>
+          <t>1224755999.99996</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1149.186</t>
+          <t>1149185999.99967</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1116.763</t>
+          <t>1116763000.00009</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1152.637</t>
+          <t>1152636999.9992</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1266.666</t>
+          <t>1266666000.0004</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1206.75</t>
+          <t>1206750000.00013</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1277.217</t>
+          <t>1277217000.00024</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1332.742</t>
+          <t>1332742000.00008</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1349.86</t>
+          <t>1349860000.00048</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1418.119</t>
+          <t>1418119000.00051</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1381.085</t>
+          <t>1381085000.00001</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1422.379</t>
+          <t>1422378999.99977</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1059.615</t>
+          <t>1059614999.99969</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>969.944</t>
+          <t>969944000.000027</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>921.764</t>
+          <t>921763999.999712</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>938.904</t>
+          <t>938904000.000226</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>943.439</t>
+          <t>943438999.999989</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1363.228</t>
+          <t>1363228275.53633</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>1325.301</t>
+          <t>1325300554.16544</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>1365.311</t>
+          <t>1365311307.64343</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>1333.555</t>
+          <t>1333554858.87187</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1379.206</t>
+          <t>1379206136.68971</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>1429.648</t>
+          <t>1429647985.31091</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>1476.889</t>
+          <t>1476889353.12059</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1536.762</t>
+          <t>1536761892.28104</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>6597.374</t>
+          <t>6597374320.34105</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5340.792</t>
+          <t>5340792000.0003</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5318.837</t>
+          <t>5318836999.99843</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>5616.757</t>
+          <t>5616756999.99844</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>5247.205</t>
+          <t>5247204999.99971</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5928.309</t>
+          <t>5928309000.00095</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6097.03</t>
+          <t>6097030000.0021</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6078.812</t>
+          <t>6078812000.00074</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>6161.091</t>
+          <t>6161090999.99878</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6065.125</t>
+          <t>6065124999.99957</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>6073.625</t>
+          <t>6073624999.99818</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6247.562</t>
+          <t>6247561999.99848</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>6373.822</t>
+          <t>6373821999.99891</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>6570.317</t>
+          <t>6570316999.99905</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>6464.209</t>
+          <t>6464209000.00093</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>6247.544</t>
+          <t>6247543999.99998</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>6353.07</t>
+          <t>6353070000.00239</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>6576.149</t>
+          <t>6576149000.00036</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>6599.813</t>
+          <t>6599813000.00131</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>7641.162</t>
+          <t>7641162201.45904</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>7259.067</t>
+          <t>7259067031.44633</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>7327.497</t>
+          <t>7327497377.12862</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>7073.056</t>
+          <t>7073056260.50807</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>7059.694</t>
+          <t>7059693712.11491</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>7031.225</t>
+          <t>7031224689.29986</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>6957.5</t>
+          <t>6957500205.41989</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>6625.671</t>
+          <t>6625671463.7823</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>45957.691</t>
+          <t>45957691300.9559</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-3895.532</t>
+          <t>-3895532000.01085</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-2692.026</t>
+          <t>-2692025999.95577</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-907.89</t>
+          <t>-907889999.999569</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-905.65</t>
+          <t>-905649999.946291</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-1686.361</t>
+          <t>-1686361000.01234</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2457.944</t>
+          <t>2457943999.99627</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-1160.758</t>
+          <t>-1160758000.05094</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1675.207</t>
+          <t>1675207000.01794</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2812.846</t>
+          <t>2812846000.03785</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>3042.446</t>
+          <t>3042446000.02082</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>6948.503</t>
+          <t>6948502999.98461</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>11521.492</t>
+          <t>11521492000.0085</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>13079.198</t>
+          <t>13079197999.9825</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>14780.236</t>
+          <t>14780235999.9981</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>13331.094</t>
+          <t>13331094000.0127</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>14524.008</t>
+          <t>14524007999.9944</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>16580.619</t>
+          <t>16580618999.9892</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>18846.871</t>
+          <t>18846870999.9925</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>40498.834</t>
+          <t>40498834464.2229</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>39248.991</t>
+          <t>39248991397.5454</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>42463.306</t>
+          <t>42463306435.0025</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>42415.49</t>
+          <t>42415489907.8573</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>40657.082</t>
+          <t>40657081513.03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>35786.701</t>
+          <t>35786700540.0537</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>35857.209</t>
+          <t>35857208843.822</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>37822.011</t>
+          <t>37822010824.7308</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>21396.9</t>
+          <t>21396900066.2578</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7479.947</t>
+          <t>7479946759.99764</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7497.218</t>
+          <t>7497217520.00165</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>7620.876</t>
+          <t>7620876119.99979</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7421.372</t>
+          <t>7421371880.00161</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6998.843</t>
+          <t>6998842759.99053</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>7600.543</t>
+          <t>7600543080.00527</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6702.546</t>
+          <t>6702545720.00431</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>5948.014</t>
+          <t>5948013760.00604</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>6007.225</t>
+          <t>6007225119.99611</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>6660.599</t>
+          <t>6660598879.99171</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>5896.482</t>
+          <t>5896482279.99458</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>5975.527</t>
+          <t>5975527480.00854</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>6429.814</t>
+          <t>6429813520.00817</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>7311.324</t>
+          <t>7311323760.00602</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>8452.238</t>
+          <t>8452238079.99259</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>8628.646</t>
+          <t>8628645999.99539</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>9218.519</t>
+          <t>9218519440.00674</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>9414.297</t>
+          <t>9414296839.99738</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>15889.465</t>
+          <t>15889465114.4487</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>16303.095</t>
+          <t>16303095407.5834</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>18605.501</t>
+          <t>18605501152.2319</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>18300.578</t>
+          <t>18300577899.2445</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19659.765</t>
+          <t>19659765080.3188</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>19615.25</t>
+          <t>19615249722.6807</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20324.384</t>
+          <t>20324384451.1966</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>20400.498</t>
+          <t>20400497593.4762</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>329500.427</t>
+          <t>329500427243.582</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>183234.3</t>
+          <t>183234300000.019</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>188225.4</t>
+          <t>188225399999.997</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>173907</t>
+          <t>173907000000.007</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>201684.3</t>
+          <t>201684299999.983</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>207681.8</t>
+          <t>207681800000.008</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>213035.8</t>
+          <t>213035799999.997</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>210703.2</t>
+          <t>210703200000.04</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>209217.5</t>
+          <t>209217500000.049</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>184073.7</t>
+          <t>184073699999.948</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>210382.9</t>
+          <t>210382900000.07</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>188604.9</t>
+          <t>188604899999.996</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>217913.1</t>
+          <t>217913099999.97</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>220613</t>
+          <t>220612999999.924</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>219801</t>
+          <t>219801000000.036</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>207679.4</t>
+          <t>207679400000.014</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>207665.6</t>
+          <t>207665600000.03</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>182694.6</t>
+          <t>182694599999.956</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>216031.7</t>
+          <t>216031699999.96</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>227636.688</t>
+          <t>227636687740.623</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>233245.291</t>
+          <t>233245291107.795</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>294241.154</t>
+          <t>294241153558.04</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>294426.494</t>
+          <t>294426493720.103</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>303041.963</t>
+          <t>303041962755.624</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>294588.389</t>
+          <t>294588389354.653</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>327978.602</t>
+          <t>327978602426.702</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>329410.298</t>
+          <t>329410298235.468</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5009868.646</t>
+          <t>5009868645972.94</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-238287.253</t>
+          <t>-238287252800.557</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-260091.912</t>
+          <t>-260091912080.894</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-271245.199</t>
+          <t>-271245198680.244</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-292851.937</t>
+          <t>-292851936639.706</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-309693.079</t>
+          <t>-309693078729.713</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-344900.639</t>
+          <t>-344900638873.668</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-356106.299</t>
+          <t>-356106298675.43</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-320702.298</t>
+          <t>-320702297735.847</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-303323.388</t>
+          <t>-303323387956.723</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-237536.435</t>
+          <t>-237536434818.011</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-245126.246</t>
+          <t>-245126245998.903</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>-114754.022</t>
+          <t>-114754021723.543</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>14445.24</t>
+          <t>14445240080.8567</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>-11089.385</t>
+          <t>-11089385110.1073</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>87505.678</t>
+          <t>87505677670.2445</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>237549.724</t>
+          <t>237549724464.341</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>75934.396</t>
+          <t>75934396148.1952</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>123918.924</t>
+          <t>123918924486.318</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>3413000.044</t>
+          <t>3413000043815.6</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>3411071.673</t>
+          <t>3411071672859.09</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>3741968.382</t>
+          <t>3741968381816.08</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>3688627.404</t>
+          <t>3688627404384.96</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3850459.319</t>
+          <t>3850459318990.41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>3910300.898</t>
+          <t>3910300898135.68</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>4227335.057</t>
+          <t>4227335057237.89</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4354920.835</t>
+          <t>4354920835403</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2947.64</t>
+          <t>2947639965.6249</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1412.625</t>
+          <t>1412624999.99946</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1560.016</t>
+          <t>1560015999.9991</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1719.726</t>
+          <t>1719726000.00062</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1891.816</t>
+          <t>1891816000.00013</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1737.141</t>
+          <t>1737140999.99836</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1949.962</t>
+          <t>1949962000.00048</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1810.398</t>
+          <t>1810398000.00109</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1860.698</t>
+          <t>1860697999.99915</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1902.033</t>
+          <t>1902033000.00068</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1991.303</t>
+          <t>1991303000.0012</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1968.565</t>
+          <t>1968565000.00013</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2745.376</t>
+          <t>2745375999.99923</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2862.115</t>
+          <t>2862115000.0002</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2756.43</t>
+          <t>2756430000.00017</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2070.397</t>
+          <t>2070397000.0001</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2220.584</t>
+          <t>2220583543.81434</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1859.314</t>
+          <t>1859313999.9988</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1844.23</t>
+          <t>1844230000.00013</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2415.338</t>
+          <t>2415337857.36785</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>2421.573</t>
+          <t>2421572922.74985</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2395.935</t>
+          <t>2395934966.1362</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2536.844</t>
+          <t>2536844375.22084</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>2480.128</t>
+          <t>2480127788.29121</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2693.562</t>
+          <t>2693562100.48825</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2729.255</t>
+          <t>2729255022.88739</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>2854.372</t>
+          <t>2854372429.73663</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>6877.29</t>
+          <t>6877290477.36579</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4443.88</t>
+          <t>4443880000.00092</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3897.107</t>
+          <t>3897107000.00013</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4391.743</t>
+          <t>4391743000.00176</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4486.604</t>
+          <t>4486603999.99959</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3948.424</t>
+          <t>3948424000.0013</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3916.299</t>
+          <t>3916299000.0012</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4250.937</t>
+          <t>4250936999.9988</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4160.643</t>
+          <t>4160642999.99989</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>4844.361</t>
+          <t>4844361000.00255</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>4366.134</t>
+          <t>4366133999.99865</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>4398.988</t>
+          <t>4398987999.99968</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>4548.187</t>
+          <t>4548186999.99935</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>5310.759</t>
+          <t>5310759000.00042</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>4509.974</t>
+          <t>4509973999.99895</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>5388.134</t>
+          <t>5388134000.00017</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>4662.976</t>
+          <t>4662975999.99994</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>5605.617</t>
+          <t>5605617000.0002</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>5657.323</t>
+          <t>5657323000.00041</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>6911.529</t>
+          <t>6911529368.1116</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>6598.581</t>
+          <t>6598580984.93676</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>7256.344</t>
+          <t>7256343611.85452</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>7217.555</t>
+          <t>7217555482.96597</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>6936.542</t>
+          <t>6936542335.02984</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>6669.713</t>
+          <t>6669712619.62948</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>7032.485</t>
+          <t>7032484578.40226</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>6819.905</t>
+          <t>6819905205.47726</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3761.578</t>
+          <t>3761577773.94317</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2991.935</t>
+          <t>2991934999.99897</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3201.736</t>
+          <t>3201735999.9999</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3383.165</t>
+          <t>3383165000.00053</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3492.403</t>
+          <t>3492402999.99986</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3571.068</t>
+          <t>3571068000.00043</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3466.248</t>
+          <t>3466247999.9997</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3482.188</t>
+          <t>3482187999.99971</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>3592.404</t>
+          <t>3592403999.99936</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>3347.189</t>
+          <t>3347189000.00015</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3355.997</t>
+          <t>3355997000.00008</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>3572.076</t>
+          <t>3572075999.99994</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>3570.838</t>
+          <t>3570838000.00105</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>3742.079</t>
+          <t>3742078999.99918</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>3651.025</t>
+          <t>3651025000.00092</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>3653.77</t>
+          <t>3653769999.9997</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>3687.283</t>
+          <t>3687283000.00129</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>3820.382</t>
+          <t>3820381999.99918</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>3918.987</t>
+          <t>3918986999.99909</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>4252.414</t>
+          <t>4252414346.69369</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>4020.262</t>
+          <t>4020261772.04557</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>3703.207</t>
+          <t>3703206609.76558</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>3551.175</t>
+          <t>3551174873.2103</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3557.714</t>
+          <t>3557714015.47493</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>3456.734</t>
+          <t>3456734429.96188</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>3486.542</t>
+          <t>3486541886.2155</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3732.784</t>
+          <t>3732783614.219</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>23872.981</t>
+          <t>23872981242.8827</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14035.335</t>
+          <t>14035334559.997</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14085.217</t>
+          <t>14085217119.9971</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>13791.339</t>
+          <t>13791338600.0014</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>12943.436</t>
+          <t>12943435959.9954</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>12559.308</t>
+          <t>12559307800.0054</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10851.051</t>
+          <t>10851050599.9908</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>10164.003</t>
+          <t>10164002680.0044</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>10622.225</t>
+          <t>10622224600.0105</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>10268.204</t>
+          <t>10268203919.9958</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>10076.245</t>
+          <t>10076245399.9911</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>9830.157</t>
+          <t>9830157479.99958</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>10422.251</t>
+          <t>10422251319.9924</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>11122.51</t>
+          <t>11122509840.0005</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>10421.22</t>
+          <t>10421220160.0043</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>9794.63</t>
+          <t>9794630039.99671</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>9035.27</t>
+          <t>9035269880.00366</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>10287.242</t>
+          <t>10287241639.998</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>10131.916</t>
+          <t>10131915560.0012</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>17518.417</t>
+          <t>17518416791.3189</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>17149.413</t>
+          <t>17149412541.0955</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>19192.046</t>
+          <t>19192046262.2005</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>18383.125</t>
+          <t>18383124942.4585</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19794.813</t>
+          <t>19794812520.576</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>20408.279</t>
+          <t>20408278908.4213</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20436.148</t>
+          <t>20436148246.9668</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>20533.754</t>
+          <t>20533754336.496</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>878615.746</t>
+          <t>878615746456.673</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-83866</t>
+          <t>-83866000000.5068</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>-97800</t>
+          <t>-97800000000.1898</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-102469</t>
+          <t>-102468999999.755</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-100492</t>
+          <t>-100492000000.15</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-101676</t>
+          <t>-101676000000.282</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-108887</t>
+          <t>-108886999999.617</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-113995</t>
+          <t>-113995000000.219</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-114512</t>
+          <t>-114511999999.976</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-100559</t>
+          <t>-100558999999.925</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-98112</t>
+          <t>-98111999999.7757</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>-82373</t>
+          <t>-82373000000.3728</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>-69760</t>
+          <t>-69759999999.7098</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>-52725</t>
+          <t>-52725000000.1353</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>-40880</t>
+          <t>-40879999999.4719</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>-58985</t>
+          <t>-58984999999.4972</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>-22299</t>
+          <t>-22298999999.5785</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>-63600</t>
+          <t>-63599999999.4159</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>-96050</t>
+          <t>-96050000000.2014</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>473758.836</t>
+          <t>473758836029.939</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>480490.444</t>
+          <t>480490443750.961</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>533886.511</t>
+          <t>533886510589.774</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>533988.354</t>
+          <t>533988353741.971</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>558401.285</t>
+          <t>558401285267.204</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>570689.117</t>
+          <t>570689116923.732</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>633523.882</t>
+          <t>633523882186.457</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>675878.117</t>
+          <t>675878117327.484</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>181663.245</t>
+          <t>181663244665.619</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>55536999999.9915</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>51895000000.0226</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>52748</t>
+          <t>52748000000.026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>52457</t>
+          <t>52457000000.096</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>57243</t>
+          <t>57242999999.9758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>59915</t>
+          <t>59915000000.0665</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>57203</t>
+          <t>57202999999.9373</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>60538</t>
+          <t>60538000000.0319</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>62649</t>
+          <t>62648999999.9901</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>64693</t>
+          <t>64692999999.9579</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>68142999999.981</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>72444</t>
+          <t>72443999999.9806</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>78094</t>
+          <t>78094000000.0182</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>81880</t>
+          <t>81880000000.0672</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>127136</t>
+          <t>127135999999.991</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>175561</t>
+          <t>175560999999.976</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>100446</t>
+          <t>100446000000.067</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>99268</t>
+          <t>99267999999.987</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>191804.544</t>
+          <t>191804544149.663</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>186635.425</t>
+          <t>186635424511.543</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>216182.202</t>
+          <t>216182201888.601</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>195592.827</t>
+          <t>195592826742.479</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>203285.643</t>
+          <t>203285642537.059</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>180192.818</t>
+          <t>180192818408.664</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>174398.905</t>
+          <t>174398904985.979</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>170788.482</t>
+          <t>170788482140.352</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>327458.67</t>
+          <t>327458669788.794</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>99575</t>
+          <t>99574999999.9012</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>98356</t>
+          <t>98355999999.9649</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>109281</t>
+          <t>109281000000.012</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>116022</t>
+          <t>116022000000.041</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>127080</t>
+          <t>127080000000.158</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>130142999999.953</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>137401</t>
+          <t>137400999999.819</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>147361</t>
+          <t>147360999999.946</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>150357</t>
+          <t>150357000000.061</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>158489</t>
+          <t>158488999999.979</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>162436</t>
+          <t>162436000000.135</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>169879</t>
+          <t>169879000000.001</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>177955</t>
+          <t>177955000000.053</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>178208</t>
+          <t>178207999999.997</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>183800</t>
+          <t>183799999999.941</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>186371</t>
+          <t>186371000000.035</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>194154999999.961</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>188961</t>
+          <t>188961000000.053</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>264467.175</t>
+          <t>264467174681.512</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>224133.017</t>
+          <t>224133017026.699</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>207310.455</t>
+          <t>207310455048.048</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>205701.244</t>
+          <t>205701243897.342</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>228525.701</t>
+          <t>228525700749.388</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>246426.094</t>
+          <t>246426094153.175</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>275030.458</t>
+          <t>275030457784.329</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>283157.683</t>
+          <t>283157683331.383</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>959758.346</t>
+          <t>959758345647.203</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>349468</t>
+          <t>349467999999.952</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>358616</t>
+          <t>358615999999.929</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>368084</t>
+          <t>368084000000.012</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>376466</t>
+          <t>376466000000.09</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>385659</t>
+          <t>385658999999.998</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>395592</t>
+          <t>395592000000.018</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>404007</t>
+          <t>404006999999.943</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>414776</t>
+          <t>414776000000.242</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>425362</t>
+          <t>425362000000.041</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>434551</t>
+          <t>434550999999.875</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>440838</t>
+          <t>440838000000.125</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>451575</t>
+          <t>451574999999.792</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>474799</t>
+          <t>474799000000.052</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>479309</t>
+          <t>479308999999.987</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>487994</t>
+          <t>487993999999.885</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>499305</t>
+          <t>499304999999.959</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>525179</t>
+          <t>525179000000.092</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>553050</t>
+          <t>553049999999.889</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>734280.063</t>
+          <t>734280063250.916</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>744089.585</t>
+          <t>744089584673.394</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>806729.156</t>
+          <t>806729156377.672</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>771291.996</t>
+          <t>771291995995.176</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>780974.335</t>
+          <t>780974334663.698</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>783977.175</t>
+          <t>783977175175.948</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>858089.37</t>
+          <t>858089369942.342</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>878220.897</t>
+          <t>878220897384.128</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>77892.274</t>
+          <t>77892274269.6009</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>21246000000.006</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22241999999.9994</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>22380000000.0017</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>22908</t>
+          <t>22907999999.9897</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>23768999999.988</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20508</t>
+          <t>20507999999.9896</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>23137</t>
+          <t>23137000000.0103</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>23772000000.0106</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>25638</t>
+          <t>25638000000.0052</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>27825999999.9928</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26344000000.01</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>29198999999.9813</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>34462999999.9965</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>36474000000.0228</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>37099999999.9853</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>42100</t>
+          <t>42099999999.9756</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>46073</t>
+          <t>46073000000.0049</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>49031000000.0401</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>71800.384</t>
+          <t>71800384352.8648</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>68839.622</t>
+          <t>68839622036.7767</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>73439.718</t>
+          <t>73439717801.6763</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>71921.899</t>
+          <t>71921898659.8856</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>71614.043</t>
+          <t>71614042506.9382</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>71455.053</t>
+          <t>71455052515.8536</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>75213.365</t>
+          <t>75213365262.1358</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>77972.882</t>
+          <t>77972882406.0216</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>abstract_labour.empe.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
